--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_03-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_03-04-2026.xlsx
@@ -571,27 +571,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff7b28a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7b25ca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7b232db2d]
+	chromedriver!(No symbol) [0x7ff7b238f0e5]
+	chromedriver!(No symbol) [0x7ff7b238c7fa]
+	chromedriver!(No symbol) [0x7ff7b2389685]
+	chromedriver!(No symbol) [0x7ff7b2388537]
+	chromedriver!(No symbol) [0x7ff7b237b186]
+	chromedriver!(No symbol) [0x7ff7b23aff8a]
+	chromedriver!(No symbol) [0x7ff7b237aa06]
+	chromedriver!(No symbol) [0x7ff7b23d3b9b]
+	chromedriver!(No symbol) [0x7ff7b2379298]
+	chromedriver!(No symbol) [0x7ff7b237a183]
+	chromedriver!GetHandleVerifier [0x7ff7b28cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7b28c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7b28e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7b25e6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7b25efacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7b25d3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7b25d37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7b25b7e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -689,27 +689,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -807,27 +807,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -925,27 +925,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -1043,27 +1043,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -1161,27 +1161,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -1279,27 +1279,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -1397,27 +1397,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -1515,27 +1515,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -1633,27 +1633,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -1751,27 +1751,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -1869,27 +1869,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -1987,27 +1987,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -2105,27 +2105,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -2223,27 +2223,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -2433,27 +2433,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -2551,27 +2551,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -2669,27 +2669,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -2787,27 +2787,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -2905,27 +2905,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -3023,27 +3023,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -3141,27 +3141,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -3259,27 +3259,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
@@ -3339,12 +3339,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£52.68</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>£52.68</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3377,27 +3377,27 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68c4129c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68c13a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff68be9db2d]
-	chromedriver!(No symbol) [0x7ff68beff0e5]
-	chromedriver!(No symbol) [0x7ff68befc7fa]
-	chromedriver!(No symbol) [0x7ff68bef9685]
-	chromedriver!(No symbol) [0x7ff68bef8537]
-	chromedriver!(No symbol) [0x7ff68beeb186]
-	chromedriver!(No symbol) [0x7ff68bf1ff8a]
-	chromedriver!(No symbol) [0x7ff68beeaa06]
-	chromedriver!(No symbol) [0x7ff68bf43b9b]
-	chromedriver!(No symbol) [0x7ff68bee9298]
-	chromedriver!(No symbol) [0x7ff68beea183]
-	chromedriver!GetHandleVerifier [0x7ff68c43de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff68c438588+313348]
-	chromedriver!GetHandleVerifier [0x7ff68c459d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff68c156785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68c15facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff68c143634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff68c1437e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff68c127e37+2bf7]
+	chromedriver!GetHandleVerifier [0x7ff6615f29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff66131a0d0+14e90]
+	chromedriver!(No symbol) [0x7ff66107db2d]
+	chromedriver!(No symbol) [0x7ff6610df0e5]
+	chromedriver!(No symbol) [0x7ff6610dc7fa]
+	chromedriver!(No symbol) [0x7ff6610d9685]
+	chromedriver!(No symbol) [0x7ff6610d8537]
+	chromedriver!(No symbol) [0x7ff6610cb186]
+	chromedriver!(No symbol) [0x7ff6610fff8a]
+	chromedriver!(No symbol) [0x7ff6610caa06]
+	chromedriver!(No symbol) [0x7ff661123b9b]
+	chromedriver!(No symbol) [0x7ff6610c9298]
+	chromedriver!(No symbol) [0x7ff6610ca183]
+	chromedriver!GetHandleVerifier [0x7ff66161de0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff661618588+313348]
+	chromedriver!GetHandleVerifier [0x7ff661639d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff661336785+31545]
+	chromedriver!GetHandleVerifier [0x7ff66133facc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff661323634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff6613237e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff661307e37+2bf7]
 	KERNEL32!BaseThreadInitThunk [0x7ff940cbe8d7+17]
 	ntdll!RtlUserThreadStart [0x7ff9419ec48c+2c]
 </t>
